--- a/stories/arbres/ATOM-REL.CON.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file. Octave dit : stop. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Octave marche vers la maîtresse. Il dit : on m'a bousculé. La maîtresse l'écoute. Le soir, maman vient. Octave raconte. Maman dit : tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
+          <t>Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file. Stop. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Octave marche vers la maîtresse. On m'a bousculé. La maîtresse l'écoute. Le soir, maman vient. Octave raconte. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file.
+enfant-m|Stop. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
+narrateur|Octave marche vers la maîtresse.
+narrateur|On m'a bousculé.
+narrateur|La maîtresse l'écoute. Le soir, maman vient. Octave raconte.
+maman|Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Octave. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Octave a dit stop. Il s'est éloigné. Il a rejoint la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend la main d'Octave. Ils marchent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 maman|Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Un camarade bouscule Octave. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Octave a dit stop. Il s'est éloigné. Il a rejoint la maîtresse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Maman prend la main d'Octave. Ils marchent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Octave dit stop dans le préau</t>
+          <t>Raphaël dit stop sous le préau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël attend sous le préau. Un camarade bouscule la file. Raphaël dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file. Stop. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Octave marche vers la maîtresse. On m'a bousculé. La maîtresse l'écoute. Le soir, maman vient. Octave raconte. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
+          <t>Le toit du préau fait des gouttes. Les gouttes tapent le zinc, une par une. Une goutte plus grosse fait tin. Des bottes jaunes brillent sous un banc. Elles sentent le caoutchouc froid. Les crochets des manteaux sentent la laine mouillée. Maman ajuste le col de Raphaël. Tu as tes boutons, Raphaël ? Oui, maman. Ils sont tous fermés. Le préau est sec, toi. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Raphaël est sous le préau. Il attend dans la file. Ses chaussures sont sur une ligne peinte. Je suis sur la ligne. La ligne est blanche et un peu usée. Raphaël compte les gouttes, tout bas. Une, deux, trois. Un camarade arrive trop vite. Il bouscule la file. Raphaël sent son épaule. Son cœur tape. Stop. Raphaël fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Raphaël marche vers la porte. Ses chaussures sonnent sur le ciment. On m'a bousculé. La maîtresse l'écoute. Raphaël reste près d'elle. Il pose une main sur le montant de la porte. Le bois est lisse et un peu froid. Je reste ici. Les gouttes tapent encore le zinc. La file redevient calme. Raphaël souffle. Son cœur tape moins vite. Le soir, maman revient. Les bottes jaunes sont encore sous le banc. Raphaël les regarde un instant. Elles brillent moins. Tu as attendu sous le préau ? Oui. Un camarade est passé trop près. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse. C'est du bon travail. Tu as entendu les gouttes, encore ? Oui. Sur le zinc. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Maman prend sa main. Une goutte tombe, une dernière, tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file.
-enfant-m|Stop. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
-narrateur|Octave marche vers la maîtresse.
-narrateur|On m'a bousculé.
-narrateur|La maîtresse l'écoute. Le soir, maman vient. Octave raconte.
-maman|Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.</t>
+          <t>narrateur|Le toit du préau fait des gouttes.
+narrateur|Les gouttes tapent le zinc, une par une.
+narrateur|Une goutte plus grosse fait tin.
+narrateur|Des bottes jaunes brillent sous un banc.
+narrateur|Elles sentent le caoutchouc froid.
+narrateur|Les crochets des manteaux sentent la laine mouillée.
+narrateur|Maman ajuste le col de Raphaël.
+maman|Tu as tes boutons, Raphaël ?
+enfant-m|Oui, maman.
+enfant-m|Ils sont tous fermés.
+maman|Le préau est sec, toi.
+maman|Je reviens ce soir.
+enfant-m|D'accord.
+narrateur|La maîtresse est près de la porte.
+narrateur|En ce moment, Raphaël est sous le préau.
+narrateur|Il attend dans la file.
+narrateur|Ses chaussures sont sur une ligne peinte.
+enfant-m|Je suis sur la ligne.
+narrateur|La ligne est blanche et un peu usée.
+narrateur|Raphaël compte les gouttes, tout bas.
+narrateur|Une, deux, trois.
+narrateur|Un camarade arrive trop vite.
+narrateur|Il bouscule la file.
+narrateur|Raphaël sent son épaule.
+narrateur|Son cœur tape.
+enfant-m|Stop.
+narrateur|Raphaël fait un pas.
+narrateur|Il peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Raphaël marche vers la porte.
+narrateur|Ses chaussures sonnent sur le ciment.
+enfant-m|On m'a bousculé.
+narrateur|La maîtresse l'écoute.
+narrateur|Raphaël reste près d'elle.
+narrateur|Il pose une main sur le montant de la porte.
+narrateur|Le bois est lisse et un peu froid.
+enfant-m|Je reste ici.
+narrateur|Les gouttes tapent encore le zinc.
+narrateur|La file redevient calme.
+narrateur|Raphaël souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le soir, maman revient.
+narrateur|Les bottes jaunes sont encore sous le banc.
+narrateur|Raphaël les regarde un instant.
+narrateur|Elles brillent moins.
+maman|Tu as attendu sous le préau ?
+enfant-m|Oui.
+enfant-m|Un camarade est passé trop près.
+enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+maman|Bravo, Raphaël.
+maman|Tu as dit stop.
+maman|Tu t'es éloigné.
+maman|Tu es allé vers la maîtresse.
+maman|C'est du bon travail.
+maman|Tu as entendu les gouttes, encore ?
+enfant-m|Oui.
+enfant-m|Sur le zinc.
+maman|Et toi, tu as su quoi faire.
+enfant-m|Stop.
+enfant-m|Puis la maîtresse.
+narrateur|Maman prend sa main.
+narrateur|Une goutte tombe, une dernière, tout bas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Octave. Que fait-il ?</t>
+          <t>Un camarade bouscule Raphaël. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Octave. Que fait-il ?</t>
+          <t>narrateur|Un camarade bouscule Raphaël.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Octave a dit stop. Il s'est éloigné. Il a rejoint la maîtresse.</t>
+          <t>Raphaël a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Stop, s'éloigner, maîtresse. J'ai dit stop. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1743,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Octave a dit stop. Il s'est éloigné. Il a rejoint la maîtresse.</t>
+          <t>narrateur|Raphaël a dit stop.
+narrateur|Il s'est éloigné.
+narrateur|Il a rejoint la maîtresse.
+maman|Bravo.
+maman|Stop, s'éloigner, maîtresse.
+enfant-m|J'ai dit stop.
+maman|Oui.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend la main d'Octave. Ils marchent.</t>
+          <t>Maman prend la main de Raphaël. On marche ? Oui, maman. Les crochets des manteaux ne bougent plus. Tes boutons sont encore fermés ? Oui. Tu entends encore le zinc ? Presque plus. Les bottes jaunes restent sous le banc. Une dernière goutte tombe, loin. Le zinc est calme, maintenant. Oui. Le col de Raphaël est encore bien fermé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1918,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend la main d'Octave. Ils marchent.</t>
+          <t>narrateur|Maman prend la main de Raphaël.
+maman|On marche ?
+enfant-m|Oui, maman.
+narrateur|Les crochets des manteaux ne bougent plus.
+maman|Tes boutons sont encore fermés ?
+enfant-m|Oui.
+maman|Tu entends encore le zinc ?
+enfant-m|Presque plus.
+narrateur|Les bottes jaunes restent sous le banc.
+narrateur|Une dernière goutte tombe, loin.
+maman|Le zinc est calme, maintenant.
+enfant-m|Oui.
+narrateur|Le col de Raphaël est encore bien fermé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as fait du bon travail. Le toit du préau est calme, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2098,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Le toit du préau est calme, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le toit du préau fait des gouttes. Les gouttes tapent le zinc, une par une. Une goutte plus grosse fait tin. Des bottes jaunes brillent sous un banc. Elles sentent le caoutchouc froid. Les crochets des manteaux sentent la laine mouillée. Maman ajuste le col de Raphaël. Tu as tes boutons, Raphaël ? Oui, maman. Ils sont tous fermés. Le préau est sec, toi. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Raphaël est sous le préau. Il attend dans la file. Ses chaussures sont sur une ligne peinte. Je suis sur la ligne. La ligne est blanche et un peu usée. Raphaël compte les gouttes, tout bas. Une, deux, trois. Un camarade arrive trop vite. Il bouscule la file. Raphaël sent son épaule. Son cœur tape. Stop. Raphaël fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Raphaël marche vers la porte. Ses chaussures sonnent sur le ciment. On m'a bousculé. La maîtresse l'écoute. Raphaël reste près d'elle. Il pose une main sur le montant de la porte. Le bois est lisse et un peu froid. Je reste ici. Les gouttes tapent encore le zinc. La file redevient calme. Raphaël souffle. Son cœur tape moins vite. Le soir, maman revient. Les bottes jaunes sont encore sous le banc. Raphaël les regarde un instant. Elles brillent moins. Tu as attendu sous le préau ? Oui. Un camarade est passé trop près. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse. C'est du bon travail. Tu as entendu les gouttes, encore ? Oui. Sur le zinc. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Maman prend sa main. Une goutte tombe, une dernière, tout bas.</t>
+          <t>Le toit du préau fait des gouttes. Les gouttes tapent le zinc, une par une. Une goutte plus grosse fait tin. Des bottes jaunes brillent sous un banc. Elles sentent le caoutchouc froid. Les crochets des manteaux sentent la laine mouillée. Maman ajuste le col de Raphaël. Tu as tes boutons, Raphaël ? Oui, maman. Ils sont tous fermés. Le préau est sec, toi. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Raphaël est sous le préau. Il attend dans la file. Ses chaussures sont sur une ligne peinte. Je suis sur la ligne. La ligne est blanche et un peu usée. Raphaël compte les gouttes, tout bas. Une, deux, trois. Un camarade arrive trop vite. Il bouscule la file. Raphaël sent son épaule. Son cœur tape. Stop. Raphaël fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Raphaël marche vers la porte. Ses chaussures sonnent sur le ciment. On m'a bousculé. La maîtresse l'écoute. Raphaël reste près d'elle. Il pose une main sur le montant de la porte. Le bois est lisse et un peu froid. Je reste ici. Les gouttes tapent encore le zinc. La file redevient calme. Raphaël souffle. Son cœur tape moins vite. Le soir, maman revient. Les bottes jaunes sont encore sous le banc. Raphaël les regarde un instant. Elles brillent moins. Tu as attendu sous le préau ? Oui. Un camarade est passé trop près. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse. Tu as entendu les gouttes, encore ? Oui. Sur le zinc. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Maman prend sa main. Une goutte tombe, une dernière, tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Octave est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file. Octave dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il fait un pas. Il doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Octave marche vers la maîtresse. Il dit : on m'a bousculé. La maîtresse l'écoute. Le soir, maman vient. Octave raconte. Maman dit : tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le toit du préau fait des gouttes. Les gouttes tapent le zinc, une par une. Une goutte plus grosse fait tin. Des bottes jaunes brillent sous un banc. Elles sentent le caoutchouc froid. Les crochets des manteaux sentent la laine mouillée. Maman ajuste le col de Raphaël. Tu as tes boutons, Raphaël ? Oui, maman. Ils sont tous fermés. Le préau est sec, toi. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Raphaël est sous le préau. Il attend dans la file. Ses chaussures sont sur une ligne peinte. Je suis sur la ligne. La ligne est blanche et un peu usée. Raphaël compte les gouttes, tout bas. Une, deux, trois. Un camarade arrive trop vite. Il bouscule la file. Raphaël sent son épaule. Son cœur tape. Stop. Raphaël fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Raphaël marche vers la porte. Ses chaussures sonnent sur le ciment. On m'a bousculé. La maîtresse l'écoute. Raphaël reste près d'elle. Il pose une main sur le montant de la porte. Le bois est lisse et un peu froid. Je reste ici. Les gouttes tapent encore le zinc. La file redevient calme. Raphaël souffle. Son cœur tape moins vite. Le soir, maman revient. Les bottes jaunes sont encore sous le banc. Raphaël les regarde un instant. Elles brillent moins. Tu as attendu sous le préau ? Oui. Un camarade est passé trop près. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as dit stop. Tu t'es éloigné. Tu es allé vers la maîtresse. Tu as entendu les gouttes, encore ? Oui. Sur le zinc. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Maman prend sa main. Une goutte tombe, une dernière, tout bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 maman|Tu as dit stop.
 maman|Tu t'es éloigné.
 maman|Tu es allé vers la maîtresse.
-maman|C'est du bon travail.
 maman|Tu as entendu les gouttes, encore ?
 enfant-m|Oui.
 enfant-m|Sur le zinc.
@@ -1389,7 +1388,6 @@
 narrateur|Une goutte tombe, une dernière, tout bas.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1419,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Octave. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Raphaël. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1572,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Stop, s'éloigner, maîtresse. J'ai dit stop. Oui. Tu as fait du bon travail.</t>
+          <t>Raphaël a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Stop, s'éloigner, maîtresse. J'ai dit stop. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Octave a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il s'est éloigné. Il a rejoint la maîtresse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Stop, s'éloigner, maîtresse. J'ai dit stop. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,11 +1746,9 @@
 maman|Bravo.
 maman|Stop, s'éloigner, maîtresse.
 enfant-m|J'ai dit stop.
-maman|Oui.
-maman|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; d'Octave. Ils marchent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman prend la main de Raphaël. On marche ? Oui, maman. Les crochets des manteaux ne bougent plus. Tes boutons sont encore fermés ? Oui. Tu entends encore le zinc ? Presque plus. Les bottes jaunes restent sous le banc. Une dernière goutte tombe, loin. Le zinc est calme, maintenant. Oui. Le col de Raphaël est encore bien fermé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,7 +1928,6 @@
 narrateur|Le col de Raphaël est encore bien fermé.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Tu as fait du bon travail. Le toit du préau est calme, maintenant. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Le toit du préau est calme, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Raphaël. Le toit du préau est calme, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2095,9 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-narrateur|Le toit du préau est calme, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le toit du préau est calme, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école</t>
+          <t>école, préau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Octave, maîtresse, maman</t>
+          <t>Raphaël, maîtresse, maman</t>
         </is>
       </c>
     </row>
